--- a/data/qa/prospect_to_cash/faq.xlsx
+++ b/data/qa/prospect_to_cash/faq.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0019</t>
+          <t>KB-0059</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,12 +564,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prospect-to-Cash</t>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -567,24 +579,20 @@
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>overview</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is the Prospect-to-Cash process?</t>
+          <t>What is the typical end-to-end process for prospect-to-cash?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Prospect-to-Cash is the end-to-end flow from an initial Prospect through Lead, Opportunity, Estimate, Quotation, Customer, Customer Order, Pricing and Credit checks, Shipment, Invoice, and finally Payment.</t>
+          <t>A common path is contact/prospect → lead → opportunity → estimate/quote → customer → customer order and lines → fulfillment/shipment → invoice → A/R payment and follow-up. This is a navigation map, not a rule requiring every record.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prospect to cash,end to end process</t>
+          <t>prospect to cash, end to end, lifecycle, CRM to cash</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -595,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>faq.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Prospect-to-Cash Cross-Process Guide &gt; End-to-end map and alternate paths</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -619,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -630,10 +640,696 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0060</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Are all steps in the prospect-to-cash process required?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>This is a navigation map, not a rule requiring every record. A lead can belong to an existing customer, an estimate can exist without a prior lead, and one order can have multiple lines, shipments, invoices, or payments. Returns and credit memos create additional branches.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>prospect to cash, alternate paths, lifecycle, order to cash</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>faq.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide &gt; End-to-end map and alternate paths</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0061</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How do I trace a customer request through the Prospect-to-Cash process in SyteLine?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>To trace a customer request, start by finding the party on Prospects or Customers and confirming contact and site. Then, find the Lead and Opportunity to inspect status, owner, tasks, and projected close date. Next, find the linked Estimate and its lines to check quote version, validity, prices, and customer response. If accepted, find the Customer and Customer Orders record, compare details, inspect each Customer Order Line, review shipment transactions and invoice history, and finally inspect A/R open items, payment applications, credit memos, and aging to determine the remaining balance.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>trace, customer request, Prospect-to-Cash, forms, process</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>faq.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide &gt; Trace one customer request through the forms</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0062</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What should I check at each stage when tracing a customer request?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>At each stage, check the party details, Lead and Opportunity status, Estimate and quote information, Customer and Customer Orders records, Customer Order Line details, shipment and invoice history, and A/R open items and payments. Record the latest customer interaction and any unresolved next action.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>check, customer request, stages, details, process</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>faq.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide &gt; Trace one customer request through the forms</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0063</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>How do I trace a customer request through the forms in Prospect-to-Cash?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Follow identifiers and quantities from party to invoice and A/R rather than treating one status as the whole answer.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>trace order, trace quote, trace invoice, related records, reconciliation</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>faq.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide &gt; Trace one customer request through the forms</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0064</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Can I answer questions about a customer's balance or order status using documentation?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Questions about customer balance or order status require an authorized live lookup; static knowledge from documents cannot provide these answers.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>customer balance, order status, live data, static knowledge</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>faq.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide &gt; How to answer common user questions</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0065</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>What information do I need to provide for a precise answer to my request?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>For an ambiguous request, you should provide the entity and identifier (such as prospect, customer, opportunity, estimate, order, line/release, shipment, invoice, payment), site, and intended action. For field help, include the form, tab, field, and any visible record context. For financial or security-sensitive questions, a current authorized lookup is required.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>clarification, form context, record ID, site, permissions</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>faq.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide &gt; What must be known before a precise answer</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0066</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>What should I do before asking about a specific workflow or status?</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Resolve the record and screen context before giving a specific workflow or factual status.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>clarification, form context, record ID, site, permissions</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>faq.md</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Prospect-to-Cash Cross-Process Guide &gt; What must be known before a precise answer</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -650,36 +1346,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
@@ -688,7 +1384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0019</t>
+          <t>KB-0059</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -698,7 +1394,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>explain the prospect to cash process</t>
+          <t>Can you describe the full prospect-to-cash process?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,17 +1404,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>auto_derived</t>
         </is>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA-0019</t>
+          <t>KB-0059</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -728,7 +1424,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>prospect to cash overview</t>
+          <t>What's the usual flow from prospect to cash?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -738,11 +1434,671 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>auto_derived</t>
         </is>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0059</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>How does the prospect-to-cash lifecycle work?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0060</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Do I have to follow every step in the prospect-to-cash process?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0060</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Is it mandatory to create every record in the process?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0060</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Can some steps be skipped in the prospect-to-cash flow?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0061</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What are the steps to follow a customer request from start to finish?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0061</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How can I track a customer order through all the forms?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0061</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What process should I use to trace a customer request in SyteLine?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0062</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What details do I need to review when tracking a customer request?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0062</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Which items should I inspect at each step of the process?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0062</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What information is important to check as I trace a customer request?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0063</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How can I track a customer request across forms?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0063</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What's the way to follow a request from start to finish?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0063</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>How do I reconcile a customer request through the process?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0064</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Can I use docs to tell a customer's balance?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0064</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Do I need live data to check order status?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0064</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Is documentation enough to answer balance questions?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0065</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>What details should I give to get an exact answer?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0065</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>How do I make sure my question gets a specific response?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0065</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>What info is needed for a clear answer?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KB-0066</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>How do I prepare before asking about a workflow?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KB-0066</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>What needs to be clear before I ask about a status?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KB-0066</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>What should I confirm before requesting workflow details?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
